--- a/output/pdf_financials_xlsx/TNR.xlsx
+++ b/output/pdf_financials_xlsx/TNR.xlsx
@@ -5910,49 +5910,49 @@
         <v>3.177323</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.109831</v>
+        <v>3.177323</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.266445</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.470381</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.487384</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.672535</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.684426</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.959584</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.055484</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.434215</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.509509</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.937699</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.108963</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.216469</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.347206</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.263838</v>
       </c>
     </row>
     <row r="93">
@@ -7398,19 +7398,19 @@
         <v>-0.106893</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>4.252695</v>
+        <v>3.726974</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>3.192629</v>
+        <v>1.402779</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.510236</v>
+        <v>1.236159</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.024254</v>
+        <v>0.000517</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>8.715297</v>
+        <v>8.651206999999999</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -9785,7 +9785,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10951,7 +10955,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11763,7 +11771,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -12266,7 +12278,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13863,7 +13879,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14267,7 +14287,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15479,7 +15503,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15887,7 +15915,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16798,7 +16830,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -18085,7 +18121,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20620,7 +20660,11 @@
           <t>Share-based payments reserve 4,266,445</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -34212,7 +34256,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TNR.xlsx
+++ b/output/pdf_financials_xlsx/TNR.xlsx
@@ -1029,25 +1029,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.025902</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003049</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003133</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000161</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.017715</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.014555</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.005841</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.02221</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.104424</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011189</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00048</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1985,25 +1985,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.430397</v>
+        <v>-2.456299</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.701775</v>
+        <v>-2.704824</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.411647</v>
+        <v>-3.41478</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.852724</v>
+        <v>-5.852885</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.81789</v>
+        <v>-5.835605</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.9472159999999999</v>
+        <v>-0.961771</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.336893</v>
+        <v>-0.342734</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-9.401998000000001</v>
@@ -2012,13 +2012,13 @@
         <v>-1.194812</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.141577</v>
+        <v>1.119367</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.012373</v>
+        <v>-3.116797</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.358324</v>
+        <v>-0.369513</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-1.957217</v>
@@ -2027,10 +2027,10 @@
         <v>-0.303678</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>7.891907</v>
+        <v>7.891427</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.015329</v>
+        <v>-1.015451</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-1.260379</v>
@@ -2101,25 +2101,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.430397</v>
+        <v>-2.456299</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.701775</v>
+        <v>-2.704824</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.411647</v>
+        <v>-3.41478</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.832834</v>
+        <v>-5.832995</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.812615</v>
+        <v>-5.83033</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.944832</v>
+        <v>-0.959387</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.336893</v>
+        <v>-0.342734</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-9.401998000000001</v>
@@ -2128,13 +2128,13 @@
         <v>-1.194812</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.141577</v>
+        <v>1.119367</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.012373</v>
+        <v>-3.116797</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.345328</v>
+        <v>-0.356517</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.957217</v>
@@ -2143,10 +2143,10 @@
         <v>-0.303678</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>7.894073</v>
+        <v>7.893593</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.015329</v>
+        <v>-1.015451</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-1.260379</v>
@@ -2408,55 +2408,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.171746</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.560789</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.559065</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.47841</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.752138</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.033751</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.00623</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.023338</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.116967</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002521</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.012742</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001855</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001091</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.233439</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.581689</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.012201</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.021328</v>
       </c>
     </row>
     <row r="35">
@@ -2524,55 +2524,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.021835</v>
+        <v>0.193581</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.00168</v>
+        <v>2.562469</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.00168</v>
+        <v>2.560745</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.02082</v>
+        <v>0.49923</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.757338</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.8759</v>
+        <v>1.909651</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.1102</v>
+        <v>1.11643</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.023338</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.116967</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.538532</v>
+        <v>1.541053</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.09341000000000001</v>
+        <v>0.106152</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.006744</v>
+        <v>0.008599000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.005978</v>
+        <v>0.007069</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.001612</v>
+        <v>0.235051</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.000217</v>
+        <v>0.581906</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.000106</v>
+        <v>0.012307</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>9.500000000000001e-05</v>
+        <v>0.021423</v>
       </c>
     </row>
     <row r="37">
@@ -3220,55 +3220,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.182656</v>
+        <v>0.01091</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.585703</v>
+        <v>0.024914</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.583979</v>
+        <v>0.024914</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.487682</v>
+        <v>0.009272000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.8621450000000001</v>
+        <v>0.110007</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.043127</v>
+        <v>0.009376000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.014886</v>
+        <v>0.008656</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.023338</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.116967</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.012961</v>
+        <v>0.01044</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.718069</v>
+        <v>0.705327</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008451</v>
+        <v>0.006596</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.270215</v>
+        <v>0.036776</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.602972</v>
+        <v>0.021283</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.070517</v>
+        <v>0.058316</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.103471</v>
+        <v>0.08214299999999999</v>
       </c>
     </row>
     <row r="49">
@@ -7770,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0138</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -7828,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0138</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -28090,7 +28090,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -51018,7 +51022,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -55265,7 +55269,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -58471,7 +58475,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -61342,7 +61346,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -66831,7 +66835,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E588" s="5" t="n">

--- a/output/pdf_financials_xlsx/TNR.xlsx
+++ b/output/pdf_financials_xlsx/TNR.xlsx
@@ -766,28 +766,28 @@
         <v>1.058336</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.034509</v>
+        <v>1.064509</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.207997</v>
+        <v>1.268929</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.094945</v>
+        <v>1.262945</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.376859</v>
+        <v>1.512601</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.551965</v>
+        <v>1.689565</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.052431</v>
+        <v>1.596431</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.541635</v>
+        <v>0.733635</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.561127</v>
+        <v>0.753127</v>
       </c>
     </row>
     <row r="8">
@@ -1325,7 +1325,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.981297</v>
+        <v>-0.125</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2257,7 +2257,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-28.76314577680516</v>
+        <v>-3.663919508671325</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6955,19 +6955,19 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.933931</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.733867</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>1.049564</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>1.208125</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.471922</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07285700000000001</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003346</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001028</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.092083</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
@@ -7218,37 +7218,37 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.110072</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.128758</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.003848</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.248027</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>2.495823</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.887063</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.855468</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.621077</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.09852900000000001</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -8351,16 +8351,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07285700000000001</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003346</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001028</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8409,16 +8409,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.22258</v>
+        <v>-1.295437</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.334179</v>
+        <v>-1.337525</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.35521</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.500566</v>
+        <v>-1.501594</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.398484</v>
@@ -23992,7 +23992,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -24708,7 +24712,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -26993,7 +27001,11 @@
           <t>Shares issued for cash 4,070,000 185,250 18,250</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -27698,7 +27710,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -27787,7 +27803,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -30290,7 +30310,11 @@
           <t>Share issued for private placement</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -30391,7 +30415,11 @@
           <t>Share issuance cost on private placement</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -37369,7 +37397,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -40989,7 +41021,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -43908,7 +43944,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>-0.07285700000000001</v>
       </c>
@@ -44308,7 +44348,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -46817,7 +46861,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -50017,7 +50065,11 @@
           <t>Directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -51814,7 +51866,11 @@
           <t>Directors’ fees (Note 8)</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -54794,7 +54850,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -69231,7 +69291,11 @@
           <t>Future income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
